--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$71</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="440">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Fr Preadmission Coverage Profile</t>
+    <t>Profil Coverage pour la préadmission FR</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T09:05:02+00:00</t>
+    <t>2025-04-24T12:12:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil FHIR pour la couverture sociale du patient pendant la préadmission</t>
+    <t>Profil Coverage pour la gestion des informations liées à la couverture sociale AMO et AMC pour la préadmission hospitalière.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -431,33 +434,57 @@
     <t>Coverage.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Coverage.extension:informationsAmc</t>
+  </si>
+  <si>
+    <t>informationsAmc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://fhir_interop.happytal.com/fhir/StructureDefinition/FrCoverageAMCExtended}
+</t>
+  </si>
+  <si>
+    <t>Extension AMC Étendue</t>
+  </si>
+  <si>
+    <t>Extension pour les données spécifiques AMC incluant nom, numéro, code convention, code CSR et datamatrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Coverage.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Coverage.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -465,6 +492,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -523,6 +553,9 @@
     <t>Need to track the status of the resource as 'draft' resources may undergo further edits while 'active' resources are immutable and may only have their status changed to 'cancelled'.</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -569,6 +602,219 @@
     <t>IN1-15</t>
   </si>
   <si>
+    <t>Coverage.type.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Coverage.type.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Coverage.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Coverage.type.coding.id</t>
+  </si>
+  <si>
+    <t>Coverage.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Coverage.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/coverage-type</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Coverage.type.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Coverage.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-couverture-sociale-vs</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Coverage.type.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Coverage.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Coverage.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Coverage.policyHolder</t>
   </si>
   <si>
@@ -603,14 +849,14 @@
     <t>Coverage.subscriber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
-    <t>Subscriber to the policy</t>
-  </si>
-  <si>
-    <t>The party who has signed-up for or 'owns' the contractual relationship to the policy or to whom the benefit of the policy for services rendered to them or their family is due.</t>
+    <t>Référence vers l’assuré</t>
+  </si>
+  <si>
+    <t>Référence vers l’assuré (et son NIR). À renseigner obligatoirement si l’assuré est différent du bénéficiaire.</t>
   </si>
   <si>
     <t>May be self or a parent in the case of dependants.</t>
@@ -622,14 +868,10 @@
     <t>Coverage.subscriberId</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>ID assigned to the subscriber</t>
-  </si>
-  <si>
-    <t>The insurer assigned ID for the Subscriber.</t>
+    <t>Numéro de sécurité sociale ou numéro d'adhérent</t>
+  </si>
+  <si>
+    <t>Contient le numéro de sécurité sociale de l'ayant droit pour une AMO ou le numéro d'adhérent pour une AMC</t>
   </si>
   <si>
     <t>The insurer requires this identifier on correspondance and claims (digital and otherwise).</t>
@@ -638,10 +880,6 @@
     <t>Coverage.beneficiary</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
-</t>
-  </si>
-  <si>
     <t>Plan beneficiary</t>
   </si>
   <si>
@@ -678,10 +916,10 @@
     <t>Coverage.relationship</t>
   </si>
   <si>
-    <t>Beneficiary relationship to the subscriber</t>
-  </si>
-  <si>
-    <t>The relationship of beneficiary (patient) to the subscriber.</t>
+    <t>Lien entre l’assuré et le bénéficiaire</t>
+  </si>
+  <si>
+    <t>À renseigner obligatoirement si l’assuré est différent du bénéficiaire pour indiquer le lien entre les deux (ex. parent, conjoint, enfant).</t>
   </si>
   <si>
     <t>Typically, an individual uses policies which are theirs (relationship='self') before policies owned by others.</t>
@@ -700,6 +938,42 @@
   </si>
   <si>
     <t>C03</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.id</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.extension</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.coding</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.coding.id</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.coding.extension</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.coding.system</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/subscriber-relationship</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.coding.version</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.coding.code</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.coding.display</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Coverage.relationship.text</t>
   </si>
   <si>
     <t>Coverage.period</t>
@@ -730,6 +1004,65 @@
     <t>IN1-12 / IN1-13</t>
   </si>
   <si>
+    <t>Coverage.period.id</t>
+  </si>
+  <si>
+    <t>Coverage.period.extension</t>
+  </si>
+  <si>
+    <t>Coverage.period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>Coverage.period.end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>./high</t>
+  </si>
+  <si>
+    <t>DR.2</t>
+  </si>
+  <si>
     <t>Coverage.payor</t>
   </si>
   <si>
@@ -784,25 +1117,7 @@
     <t>Coverage.class.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Coverage.class.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Coverage.class.modifierExtension</t>
@@ -1027,10 +1342,6 @@
   </si>
   <si>
     <t>Coverage.subrogation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
   </si>
   <si>
     <t>Reimbursement to insurer</t>
@@ -1190,6 +1501,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1371,12 +1697,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP44"/>
+  <dimension ref="A1:AP71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.9296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.9296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.28515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1384,7 +1710,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="38.19921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="75.4765625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1399,10 +1725,10 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.9140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="36.69140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -1410,7 +1736,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.890625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="50.96484375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="43.95703125" customWidth="true" bestFit="true"/>
@@ -1545,7 +1871,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1665,7 +1991,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -1785,7 +2111,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -1903,7 +2229,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>103</v>
       </c>
@@ -2023,7 +2349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>109</v>
       </c>
@@ -2143,7 +2469,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -2263,7 +2589,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2383,7 +2709,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -2392,7 +2718,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2411,17 +2737,15 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>80</v>
@@ -2458,16 +2782,14 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>140</v>
@@ -2488,7 +2810,7 @@
         <v>80</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>80</v>
@@ -2503,48 +2825,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>80</v>
       </c>
@@ -2592,7 +2912,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -2601,7 +2921,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -2610,7 +2930,7 @@
         <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>80</v>
@@ -2625,16 +2945,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2647,25 +2967,25 @@
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -2714,7 +3034,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -2726,33 +3046,33 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="AM11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP11" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>159</v>
-      </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2766,28 +3086,28 @@
         <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -2812,13 +3132,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -2836,13 +3156,13 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>80</v>
@@ -2851,30 +3171,30 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AP12" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2882,32 +3202,34 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="O13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -2917,7 +3239,7 @@
         <v>80</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>80</v>
@@ -2932,14 +3254,14 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
       </c>
@@ -2956,10 +3278,10 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>90</v>
@@ -2971,25 +3293,25 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>179</v>
       </c>
@@ -3002,13 +3324,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -3025,11 +3347,9 @@
       <c r="M14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3054,13 +3374,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3099,24 +3419,24 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>187</v>
       </c>
       <c r="AP14" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
+      <c r="A15" t="s" s="2">
         <v>188</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>189</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3136,23 +3456,19 @@
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>194</v>
-      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
       </c>
@@ -3200,7 +3516,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3212,44 +3528,44 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -3258,21 +3574,21 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" t="s" s="2">
-        <v>199</v>
-      </c>
+      <c r="N16" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
@@ -3308,57 +3624,57 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3381,15 +3697,17 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
         <v>204</v>
       </c>
@@ -3440,13 +3758,13 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
@@ -3455,30 +3773,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3498,23 +3816,19 @@
         <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
       </c>
@@ -3562,7 +3876,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3574,44 +3888,44 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>212</v>
+        <v>80</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>80</v>
@@ -3623,20 +3937,18 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -3660,55 +3972,55 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>219</v>
+        <v>80</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
@@ -3717,12 +4029,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3745,17 +4057,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3765,7 +4079,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -3804,7 +4118,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -3819,30 +4133,30 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>229</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3850,10 +4164,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>80</v>
@@ -3865,20 +4179,18 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -3926,13 +4238,13 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
@@ -3944,27 +4256,27 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>238</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>240</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3975,7 +4287,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -3984,22 +4296,20 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4024,13 +4334,11 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4048,13 +4356,13 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
@@ -4066,7 +4374,7 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>80</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
@@ -4075,18 +4383,18 @@
         <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4106,19 +4414,21 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4166,7 +4476,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4178,13 +4488,13 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>80</v>
@@ -4193,29 +4503,29 @@
         <v>80</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4224,21 +4534,23 @@
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>136</v>
+        <v>242</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4286,25 +4598,25 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>80</v>
@@ -4313,53 +4625,53 @@
         <v>80</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>139</v>
+        <v>253</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4408,25 +4720,25 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>133</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>
@@ -4435,18 +4747,18 @@
         <v>80</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4454,7 +4766,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -4469,15 +4781,17 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>171</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>263</v>
       </c>
@@ -4504,13 +4818,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>265</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4528,10 +4842,10 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -4549,24 +4863,24 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4580,7 +4894,7 @@
         <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
@@ -4589,19 +4903,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>196</v>
+        <v>269</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4650,10 +4964,10 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>90</v>
@@ -4671,19 +4985,19 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>274</v>
       </c>
@@ -4696,7 +5010,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
@@ -4711,7 +5025,7 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>275</v>
@@ -4791,19 +5105,19 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>278</v>
       </c>
@@ -4816,13 +5130,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>80</v>
@@ -4831,17 +5145,17 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -4893,7 +5207,7 @@
         <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>90</v>
@@ -4905,25 +5219,25 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>212</v>
+        <v>266</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>283</v>
       </c>
@@ -4951,7 +5265,7 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>284</v>
@@ -4959,9 +5273,11 @@
       <c r="M30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N30" s="2"/>
+      <c r="N30" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5034,32 +5350,32 @@
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -5071,19 +5387,19 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>242</v>
+        <v>180</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5108,13 +5424,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5132,13 +5448,13 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
@@ -5156,7 +5472,7 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -5165,12 +5481,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5193,13 +5509,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>248</v>
+        <v>190</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>249</v>
+        <v>191</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5250,7 +5566,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5268,7 +5584,7 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
@@ -5283,16 +5599,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5311,16 +5627,16 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5358,19 +5674,19 @@
         <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5388,7 +5704,7 @@
         <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
@@ -5403,47 +5719,47 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>139</v>
+        <v>203</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5492,7 +5808,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5504,13 +5820,13 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
@@ -5519,18 +5835,18 @@
         <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5550,23 +5866,19 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>298</v>
+        <v>190</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -5590,80 +5902,80 @@
         <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="Z35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AA35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -5672,23 +5984,21 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>305</v>
+        <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>306</v>
+        <v>195</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>307</v>
+        <v>196</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5724,57 +6034,57 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP36" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AG36" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5785,7 +6095,7 @@
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
@@ -5794,20 +6104,22 @@
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>311</v>
+        <v>211</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>293</v>
+        <v>214</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -5817,7 +6129,7 @@
         <v>80</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>80</v>
@@ -5856,13 +6168,13 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>216</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
@@ -5874,7 +6186,7 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
@@ -5883,18 +6195,18 @@
         <v>80</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5914,18 +6226,20 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -5974,7 +6288,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5986,13 +6300,13 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
@@ -6001,29 +6315,29 @@
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -6032,21 +6346,21 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>137</v>
+        <v>227</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6094,25 +6408,25 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
@@ -6121,53 +6435,51 @@
         <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>145</v>
+        <v>237</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6216,25 +6528,25 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
@@ -6243,18 +6555,18 @@
         <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6262,7 +6574,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -6277,17 +6589,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>317</v>
+        <v>243</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>319</v>
+        <v>246</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6312,13 +6626,13 @@
         <v>80</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>321</v>
+        <v>80</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
@@ -6336,10 +6650,10 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>316</v>
+        <v>247</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>90</v>
@@ -6354,7 +6668,7 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
@@ -6363,18 +6677,18 @@
         <v>80</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6397,17 +6711,19 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>324</v>
+        <v>251</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>326</v>
+        <v>254</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -6456,7 +6772,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>323</v>
+        <v>255</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6474,7 +6790,7 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
@@ -6483,18 +6799,18 @@
         <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6514,22 +6830,20 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -6578,7 +6892,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6593,30 +6907,30 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>80</v>
+        <v>316</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>80</v>
+        <v>318</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>80</v>
+        <v>319</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6627,7 +6941,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -6639,18 +6953,16 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>334</v>
+        <v>189</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>335</v>
+        <v>190</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>336</v>
+        <v>191</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>337</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -6698,40 +7010,3314 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AG44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH44" t="s" s="2">
+      <c r="N47" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q47" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="R47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G48" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AI44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
+      <c r="H48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>188</v>
+      <c r="AK48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP71">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI70">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -464,7 +464,7 @@
     <t>informationsAmc</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://fhir_interop.happytal.com/fhir/StructureDefinition/FrCoverageAMCExtended}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/fr-coverage-amc-extended}
 </t>
   </si>
   <si>
@@ -849,7 +849,7 @@
     <t>Coverage.subscriber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
 </t>
   </si>
   <si>
@@ -1710,7 +1710,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.4765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-coverage-fr</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-coverage-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -464,7 +464,7 @@
     <t>informationsAmc</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/fr-coverage-amc-extended}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/fr-coverage-amc-extended}
 </t>
   </si>
   <si>
@@ -730,7 +730,7 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-couverture-sociale-vs</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/type-couverture-sociale-vs</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1710,7 +1710,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.0625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="92.8046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1725,7 +1725,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.9140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.65625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -849,7 +849,7 @@
     <t>Coverage.subscriber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-coverage-fr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-coverage-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -464,7 +464,7 @@
     <t>informationsAmc</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/fr-coverage-amc-extended}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/fr-coverage-amc-extended}
 </t>
   </si>
   <si>
@@ -730,7 +730,7 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/type-couverture-sociale-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-couverture-sociale-vs</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1710,7 +1710,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="92.8046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1725,7 +1725,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.65625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.9140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T10:41:02+00:00</t>
+    <t>2025-05-05T08:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$60</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="413">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Profil Coverage pour la préadmission FR</t>
+    <t>Fr Preadmission Coverage Profile</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil Coverage pour la gestion des informations liées à la couverture sociale AMO et AMC pour la préadmission hospitalière.</t>
+    <t>Profil Coverage pour les couvertures sociales lors de la préadmission</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -468,10 +468,10 @@
 </t>
   </si>
   <si>
-    <t>Extension AMC Étendue</t>
-  </si>
-  <si>
-    <t>Extension pour les données spécifiques AMC incluant nom, numéro, code convention, code CSR et datamatrix</t>
+    <t>Informations AMC</t>
+  </si>
+  <si>
+    <t>Extension pour les informations AMC étendues</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -685,9 +685,6 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/coverage-type</t>
-  </si>
-  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -849,37 +846,41 @@
     <t>Coverage.subscriber</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Référence vers l’assuré</t>
+  </si>
+  <si>
+    <t>Référence vers l’assuré (et son NIR). À renseigner obligatoirement si l’assuré est différent du bénéficiaire.</t>
+  </si>
+  <si>
+    <t>May be self or a parent in the case of dependants.</t>
+  </si>
+  <si>
+    <t>This is the party who is entitled to the benfits under the policy.</t>
+  </si>
+  <si>
+    <t>Coverage.subscriberId</t>
+  </si>
+  <si>
+    <t>Numéro de sécurité sociale ou numéro d'adhérent</t>
+  </si>
+  <si>
+    <t>Contient le numéro de sécurité sociale de l'ayant droit pour une AMO ou le numéro d'adhérent pour une AMC</t>
+  </si>
+  <si>
+    <t>The insurer requires this identifier on correspondance and claims (digital and otherwise).</t>
+  </si>
+  <si>
+    <t>Coverage.beneficiary</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
-    <t>Référence vers l’assuré</t>
-  </si>
-  <si>
-    <t>Référence vers l’assuré (et son NIR). À renseigner obligatoirement si l’assuré est différent du bénéficiaire.</t>
-  </si>
-  <si>
-    <t>May be self or a parent in the case of dependants.</t>
-  </si>
-  <si>
-    <t>This is the party who is entitled to the benfits under the policy.</t>
-  </si>
-  <si>
-    <t>Coverage.subscriberId</t>
-  </si>
-  <si>
-    <t>Numéro de sécurité sociale ou numéro d'adhérent</t>
-  </si>
-  <si>
-    <t>Contient le numéro de sécurité sociale de l'ayant droit pour une AMO ou le numéro d'adhérent pour une AMC</t>
-  </si>
-  <si>
-    <t>The insurer requires this identifier on correspondance and claims (digital and otherwise).</t>
-  </si>
-  <si>
-    <t>Coverage.beneficiary</t>
-  </si>
-  <si>
     <t>Plan beneficiary</t>
   </si>
   <si>
@@ -947,30 +948,6 @@
   </si>
   <si>
     <t>Coverage.relationship.coding</t>
-  </si>
-  <si>
-    <t>Coverage.relationship.coding.id</t>
-  </si>
-  <si>
-    <t>Coverage.relationship.coding.extension</t>
-  </si>
-  <si>
-    <t>Coverage.relationship.coding.system</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/subscriber-relationship</t>
-  </si>
-  <si>
-    <t>Coverage.relationship.coding.version</t>
-  </si>
-  <si>
-    <t>Coverage.relationship.coding.code</t>
-  </si>
-  <si>
-    <t>Coverage.relationship.coding.display</t>
-  </si>
-  <si>
-    <t>Coverage.relationship.coding.userSelected</t>
   </si>
   <si>
     <t>Coverage.relationship.text</t>
@@ -1002,65 +979,6 @@
   </si>
   <si>
     <t>IN1-12 / IN1-13</t>
-  </si>
-  <si>
-    <t>Coverage.period.id</t>
-  </si>
-  <si>
-    <t>Coverage.period.extension</t>
-  </si>
-  <si>
-    <t>Coverage.period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-1
-</t>
-  </si>
-  <si>
-    <t>./low</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>Coverage.period.end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>./high</t>
-  </si>
-  <si>
-    <t>DR.2</t>
   </si>
   <si>
     <t>Coverage.payor</t>
@@ -1697,7 +1615,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP71"/>
+  <dimension ref="A1:AP60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.9296875" customWidth="true" bestFit="true"/>
@@ -4079,46 +3997,46 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4136,16 +4054,16 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
@@ -4153,10 +4071,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4182,13 +4100,13 @@
         <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4238,7 +4156,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4256,16 +4174,16 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4273,10 +4191,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4302,14 +4220,14 @@
         <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4338,25 +4256,25 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4374,16 +4292,16 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -4391,10 +4309,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4420,14 +4338,14 @@
         <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4476,7 +4394,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4494,16 +4412,16 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -4511,10 +4429,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4537,19 +4455,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4598,7 +4516,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4616,16 +4534,16 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -4633,10 +4551,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4662,16 +4580,16 @@
         <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4720,7 +4638,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4738,16 +4656,16 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -4755,10 +4673,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4781,19 +4699,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4842,7 +4760,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4863,24 +4781,24 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4903,19 +4821,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4964,7 +4882,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4985,24 +4903,24 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5028,14 +4946,14 @@
         <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5084,7 +5002,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5105,24 +5023,24 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5145,7 +5063,7 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>279</v>
@@ -5204,7 +5122,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>90</v>
@@ -5225,16 +5143,16 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -5866,19 +5784,23 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -5926,7 +5848,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5938,13 +5860,13 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>193</v>
+        <v>255</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>80</v>
@@ -5953,7 +5875,7 @@
         <v>80</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -5968,14 +5890,14 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -5984,21 +5906,21 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>304</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>195</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6034,46 +5956,46 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>198</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>80</v>
+        <v>308</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>193</v>
+        <v>309</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>80</v>
+        <v>311</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
@@ -6081,10 +6003,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6092,10 +6014,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
@@ -6107,19 +6029,19 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>104</v>
+        <v>313</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>211</v>
+        <v>314</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>213</v>
+        <v>316</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>214</v>
+        <v>317</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6129,7 +6051,7 @@
         <v>80</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>80</v>
@@ -6168,13 +6090,13 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>216</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
@@ -6186,27 +6108,27 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>217</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
+        <v>318</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>80</v>
+        <v>319</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>218</v>
+        <v>320</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>80</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6217,7 +6139,7 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -6226,21 +6148,23 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>220</v>
+        <v>324</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>221</v>
+        <v>325</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6288,13 +6212,13 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>223</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
@@ -6306,7 +6230,7 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
@@ -6315,7 +6239,7 @@
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6323,10 +6247,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6346,21 +6270,19 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6408,7 +6330,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6420,13 +6342,13 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
@@ -6435,7 +6357,7 @@
         <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6443,21 +6365,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6466,21 +6388,21 @@
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6528,25 +6450,25 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>239</v>
+        <v>193</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
@@ -6555,7 +6477,7 @@
         <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6563,45 +6485,45 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>244</v>
+        <v>333</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>245</v>
+        <v>152</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6650,25 +6572,25 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>247</v>
+        <v>334</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>248</v>
+        <v>133</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
@@ -6677,7 +6599,7 @@
         <v>80</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6685,10 +6607,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6696,7 +6618,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
@@ -6711,19 +6633,17 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>251</v>
+        <v>336</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>254</v>
+        <v>338</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -6748,13 +6668,13 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
@@ -6772,10 +6692,10 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>255</v>
+        <v>335</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -6790,7 +6710,7 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
@@ -6799,7 +6719,7 @@
         <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -6807,10 +6727,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6818,7 +6738,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -6833,17 +6753,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>312</v>
+        <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -6892,10 +6814,10 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>90</v>
@@ -6907,30 +6829,30 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>317</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>80</v>
+        <v>348</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6950,19 +6872,21 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>190</v>
+        <v>350</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>191</v>
+        <v>351</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7010,7 +6934,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>192</v>
+        <v>349</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7022,44 +6946,44 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>80</v>
+        <v>348</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7068,21 +6992,21 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>135</v>
+        <v>354</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>195</v>
+        <v>355</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7118,37 +7042,37 @@
         <v>80</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>198</v>
+        <v>353</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
@@ -7157,7 +7081,7 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7165,10 +7089,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7176,13 +7100,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>80</v>
@@ -7191,18 +7115,18 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>323</v>
+        <v>189</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7250,7 +7174,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7259,7 +7183,7 @@
         <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>328</v>
+        <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>102</v>
@@ -7268,16 +7192,16 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7285,50 +7209,50 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>323</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q47" t="s" s="2">
-        <v>335</v>
-      </c>
+      <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7372,16 +7296,16 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>328</v>
+        <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -7390,7 +7314,7 @@
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7399,7 +7323,7 @@
         <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>338</v>
+        <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7407,10 +7331,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7418,10 +7342,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7430,23 +7354,19 @@
         <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>340</v>
+        <v>189</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>341</v>
+        <v>190</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7494,49 +7414,49 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>339</v>
+        <v>192</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>345</v>
+        <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>348</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7555,20 +7475,18 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>350</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
+        <v>195</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>352</v>
+        <v>196</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7616,7 +7534,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>349</v>
+        <v>198</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7628,13 +7546,13 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
@@ -7651,42 +7569,46 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>190</v>
+        <v>332</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
       </c>
@@ -7734,25 +7656,25 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>192</v>
+        <v>334</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
@@ -7769,21 +7691,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -7792,21 +7714,23 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>195</v>
+        <v>373</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>196</v>
+        <v>374</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7830,13 +7754,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>80</v>
+        <v>377</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -7854,25 +7778,25 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>198</v>
+        <v>372</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
@@ -7889,45 +7813,45 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>358</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>135</v>
+        <v>380</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>152</v>
+        <v>383</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>153</v>
+        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7976,45 +7900,45 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>80</v>
+        <v>348</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8022,10 +7946,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8034,20 +7958,20 @@
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>180</v>
+        <v>323</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8072,13 +7996,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>295</v>
+        <v>80</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8096,13 +8020,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -8131,10 +8055,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8142,7 +8066,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>90</v>
@@ -8154,23 +8078,19 @@
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>369</v>
+        <v>190</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8218,10 +8138,10 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>368</v>
+        <v>192</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>90</v>
@@ -8230,44 +8150,44 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>373</v>
+        <v>80</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>375</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>80</v>
@@ -8276,21 +8196,21 @@
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>377</v>
+        <v>195</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8338,78 +8258,80 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>376</v>
+        <v>198</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>373</v>
+        <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>375</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>381</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>382</v>
+        <v>332</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>384</v>
+        <v>153</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8458,25 +8380,25 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>380</v>
+        <v>334</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
@@ -8485,7 +8407,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8493,10 +8415,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8504,7 +8426,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>90</v>
@@ -8519,17 +8441,17 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8554,13 +8476,13 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>80</v>
+        <v>396</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -8578,10 +8500,10 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>90</v>
@@ -8602,7 +8524,7 @@
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>389</v>
+        <v>80</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -8613,21 +8535,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>391</v>
+        <v>80</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -8636,22 +8558,20 @@
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>350</v>
+        <v>304</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8700,13 +8620,13 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
@@ -8735,10 +8655,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8761,16 +8681,20 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>190</v>
+        <v>403</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8818,7 +8742,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>192</v>
+        <v>402</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8830,13 +8754,13 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
@@ -8853,14 +8777,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8879,18 +8803,18 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>135</v>
+        <v>408</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>195</v>
+        <v>409</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8938,7 +8862,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>198</v>
+        <v>407</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -8950,7 +8874,7 @@
         <v>80</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>80</v>
@@ -8962,1345 +8886,17 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP71">
+  <autoFilter ref="A1:AP60">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10310,7 +8906,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI59">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-coverage-fr.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="412">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,7 +471,7 @@
     <t>Informations AMC</t>
   </si>
   <si>
-    <t>Extension pour les informations AMC étendues</t>
+    <t>Extension pour les informations AMC étendues issues de l'attestation harmonisée / DataMatrix AMC</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -551,9 +551,6 @@
   </si>
   <si>
     <t>Need to track the status of the resource as 'draft' resources may undergo further edits while 'active' resources are immutable and may only have their status changed to 'cancelled'.</t>
-  </si>
-  <si>
-    <t>active</t>
   </si>
   <si>
     <t>required</t>
@@ -3157,28 +3154,28 @@
         <v>80</v>
       </c>
       <c r="S13" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="T13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X13" t="s" s="2">
+      <c r="Y13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3211,13 +3208,13 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
@@ -3231,10 +3228,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3257,17 +3254,17 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3295,11 +3292,11 @@
         <v>114</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3316,7 +3313,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3337,13 +3334,13 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>80</v>
@@ -3351,10 +3348,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3377,13 +3374,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3434,25 +3431,25 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>80</v>
@@ -3469,10 +3466,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3498,10 +3495,10 @@
         <v>135</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>152</v>
@@ -3545,7 +3542,7 @@
         <v>138</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
@@ -3554,7 +3551,7 @@
         <v>139</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3572,7 +3569,7 @@
         <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>80</v>
@@ -3589,10 +3586,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3615,19 +3612,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3676,7 +3673,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3694,16 +3691,16 @@
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -3711,10 +3708,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3737,13 +3734,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3794,25 +3791,25 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
@@ -3829,10 +3826,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3858,10 +3855,10 @@
         <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>152</v>
@@ -3905,7 +3902,7 @@
         <v>138</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>80</v>
@@ -3914,7 +3911,7 @@
         <v>139</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -3932,7 +3929,7 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>80</v>
@@ -3949,10 +3946,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3978,16 +3975,16 @@
         <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4036,7 +4033,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4054,16 +4051,16 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
@@ -4071,10 +4068,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4097,16 +4094,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4156,7 +4153,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4174,16 +4171,16 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4191,10 +4188,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4220,14 +4217,14 @@
         <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4252,29 +4249,29 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4292,16 +4289,16 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -4309,10 +4306,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4335,17 +4332,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4394,7 +4391,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4412,16 +4409,16 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -4429,10 +4426,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4455,19 +4452,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4516,7 +4513,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4534,16 +4531,16 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -4551,10 +4548,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4577,19 +4574,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4638,7 +4635,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4656,16 +4653,16 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -4673,10 +4670,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4699,19 +4696,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4760,7 +4757,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4781,24 +4778,24 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>266</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4821,19 +4818,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4882,7 +4879,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4903,24 +4900,24 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>266</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4943,17 +4940,17 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5002,7 +4999,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5023,24 +5020,24 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>266</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5063,17 +5060,17 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5122,7 +5119,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>90</v>
@@ -5137,30 +5134,30 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>266</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5183,19 +5180,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5244,7 +5241,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5268,10 +5265,10 @@
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5279,10 +5276,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5305,19 +5302,19 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5342,14 +5339,14 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Y31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="Y31" t="s" s="2">
+      <c r="Z31" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5366,7 +5363,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5390,7 +5387,7 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -5401,10 +5398,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5427,13 +5424,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5484,25 +5481,25 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
@@ -5519,10 +5516,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5548,10 +5545,10 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>152</v>
@@ -5595,7 +5592,7 @@
         <v>138</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>80</v>
@@ -5604,7 +5601,7 @@
         <v>139</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5622,7 +5619,7 @@
         <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
@@ -5639,10 +5636,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5665,19 +5662,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5726,7 +5723,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5744,16 +5741,16 @@
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5761,10 +5758,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5787,19 +5784,19 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5848,7 +5845,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5866,16 +5863,16 @@
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -5883,10 +5880,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5909,17 +5906,17 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -5968,7 +5965,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5983,19 +5980,19 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
@@ -6003,10 +6000,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6029,19 +6026,19 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6090,7 +6087,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>90</v>
@@ -6111,24 +6108,24 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6151,19 +6148,19 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6212,7 +6209,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6247,10 +6244,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6273,13 +6270,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6330,25 +6327,25 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
@@ -6365,10 +6362,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6394,10 +6391,10 @@
         <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>152</v>
@@ -6450,7 +6447,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6468,7 +6465,7 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
@@ -6485,14 +6482,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6514,10 +6511,10 @@
         <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>152</v>
@@ -6572,7 +6569,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6607,10 +6604,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6633,17 +6630,17 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -6668,14 +6665,14 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="Z42" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6692,7 +6689,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>90</v>
@@ -6727,10 +6724,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6753,19 +6750,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -6814,7 +6811,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>90</v>
@@ -6838,21 +6835,21 @@
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>348</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6875,17 +6872,17 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6934,7 +6931,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6958,21 +6955,21 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>348</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6995,17 +6992,17 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7054,7 +7051,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7081,7 +7078,7 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7089,10 +7086,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7115,17 +7112,17 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7174,7 +7171,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7198,7 +7195,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7209,14 +7206,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7235,19 +7232,19 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7296,7 +7293,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7331,10 +7328,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7357,13 +7354,13 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7414,25 +7411,25 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
@@ -7449,10 +7446,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7478,10 +7475,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>152</v>
@@ -7534,7 +7531,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7552,7 +7549,7 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
@@ -7569,14 +7566,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7598,10 +7595,10 @@
         <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>152</v>
@@ -7656,7 +7653,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7691,10 +7688,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7717,19 +7714,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7754,14 +7751,14 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7778,7 +7775,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7813,10 +7810,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7839,19 +7836,19 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7900,7 +7897,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>90</v>
@@ -7924,21 +7921,21 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>348</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7961,17 +7958,17 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8020,7 +8017,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8055,10 +8052,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8081,13 +8078,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8138,25 +8135,25 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8173,10 +8170,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8202,10 +8199,10 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>152</v>
@@ -8258,7 +8255,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8276,7 +8273,7 @@
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8293,14 +8290,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8322,10 +8319,10 @@
         <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>152</v>
@@ -8380,7 +8377,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8415,10 +8412,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8441,17 +8438,17 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8476,14 +8473,14 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Z57" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8500,7 +8497,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>90</v>
@@ -8535,10 +8532,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8561,17 +8558,17 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8620,7 +8617,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8655,10 +8652,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8681,19 +8678,19 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8742,7 +8739,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8777,10 +8774,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8803,17 +8800,17 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -8862,7 +8859,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -8880,19 +8877,19 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
